--- a/NIFTY_100_Technical_Metrics.xlsx
+++ b/NIFTY_100_Technical_Metrics.xlsx
@@ -1740,7 +1740,7 @@
         <v>96</v>
       </c>
       <c r="P4">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Q4">
         <v>3156.26</v>
@@ -1856,7 +1856,7 @@
         <v>98</v>
       </c>
       <c r="P5">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q5">
         <v>1538.96</v>
@@ -1972,7 +1972,7 @@
         <v>92</v>
       </c>
       <c r="P6">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q6">
         <v>1858</v>
@@ -2088,7 +2088,7 @@
         <v>97</v>
       </c>
       <c r="P7">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q7">
         <v>223.75</v>
@@ -2204,7 +2204,7 @@
         <v>16</v>
       </c>
       <c r="P8">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Q8">
         <v>431.29</v>
@@ -2320,7 +2320,7 @@
         <v>86</v>
       </c>
       <c r="P9">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q9">
         <v>8756.700000000001</v>
@@ -2436,7 +2436,7 @@
         <v>83</v>
       </c>
       <c r="P10">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="Q10">
         <v>2714.44</v>
@@ -2552,7 +2552,7 @@
         <v>61</v>
       </c>
       <c r="P11">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="Q11">
         <v>1352.24</v>
@@ -2784,7 +2784,7 @@
         <v>45</v>
       </c>
       <c r="P13">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q13">
         <v>1844.94</v>
@@ -2900,7 +2900,7 @@
         <v>30</v>
       </c>
       <c r="P14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q14">
         <v>10867.6</v>
@@ -3016,7 +3016,7 @@
         <v>80</v>
       </c>
       <c r="P15">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q15">
         <v>1020.17</v>
@@ -3132,7 +3132,7 @@
         <v>29</v>
       </c>
       <c r="P16">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q16">
         <v>261.74</v>
@@ -3364,7 +3364,7 @@
         <v>33</v>
       </c>
       <c r="P18">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="Q18">
         <v>1883.76</v>
@@ -3480,7 +3480,7 @@
         <v>90</v>
       </c>
       <c r="P19">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="Q19">
         <v>41198</v>
@@ -3596,7 +3596,7 @@
         <v>47</v>
       </c>
       <c r="P20">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q20">
         <v>306.9</v>
@@ -3712,7 +3712,7 @@
         <v>21</v>
       </c>
       <c r="P21">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q21">
         <v>5308.1</v>
@@ -3828,7 +3828,7 @@
         <v>49</v>
       </c>
       <c r="P22">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q22">
         <v>126.56</v>
@@ -3944,7 +3944,7 @@
         <v>89</v>
       </c>
       <c r="P23">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q23">
         <v>934.63</v>
@@ -4060,7 +4060,7 @@
         <v>87</v>
       </c>
       <c r="P24">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q24">
         <v>1792.24</v>
@@ -4176,7 +4176,7 @@
         <v>59</v>
       </c>
       <c r="P25">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q25">
         <v>1458.9</v>
@@ -4408,7 +4408,7 @@
         <v>94</v>
       </c>
       <c r="P27">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Q27">
         <v>5571.4</v>
@@ -4524,7 +4524,7 @@
         <v>51</v>
       </c>
       <c r="P28">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q28">
         <v>6664.2</v>
@@ -4640,7 +4640,7 @@
         <v>53</v>
       </c>
       <c r="P29">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Q29">
         <v>655.75</v>
@@ -4756,7 +4756,7 @@
         <v>13</v>
       </c>
       <c r="P30">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q30">
         <v>4177.02</v>
@@ -4872,7 +4872,7 @@
         <v>63</v>
       </c>
       <c r="P31">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q31">
         <v>1358.18</v>
@@ -4988,7 +4988,7 @@
         <v>84</v>
       </c>
       <c r="P32">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q32">
         <v>7228.3</v>
@@ -5220,7 +5220,7 @@
         <v>72</v>
       </c>
       <c r="P34">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q34">
         <v>277.46</v>
@@ -5336,7 +5336,7 @@
         <v>56</v>
       </c>
       <c r="P35">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Q35">
         <v>174.29</v>
@@ -5452,7 +5452,7 @@
         <v>43</v>
       </c>
       <c r="P36">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q36">
         <v>1061.66</v>
@@ -5568,7 +5568,7 @@
         <v>79</v>
       </c>
       <c r="P37">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q37">
         <v>3160.7</v>
@@ -5800,7 +5800,7 @@
         <v>5</v>
       </c>
       <c r="P39">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q39">
         <v>1092.42</v>
@@ -5916,7 +5916,7 @@
         <v>78</v>
       </c>
       <c r="P40">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Q40">
         <v>2751.8</v>
@@ -6032,7 +6032,7 @@
         <v>18</v>
       </c>
       <c r="P41">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q41">
         <v>798.42</v>
@@ -6148,7 +6148,7 @@
         <v>10</v>
       </c>
       <c r="P42">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q42">
         <v>570.51</v>
@@ -6264,7 +6264,7 @@
         <v>74</v>
       </c>
       <c r="P43">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Q43">
         <v>950.38</v>
@@ -6380,7 +6380,7 @@
         <v>35</v>
       </c>
       <c r="P44">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q44">
         <v>2182.64</v>
@@ -6496,7 +6496,7 @@
         <v>55</v>
       </c>
       <c r="P45">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="Q45">
         <v>531.87</v>
@@ -6612,7 +6612,7 @@
         <v>42</v>
       </c>
       <c r="P46">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q46">
         <v>1952.26</v>
@@ -6844,7 +6844,7 @@
         <v>60</v>
       </c>
       <c r="P48">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="Q48">
         <v>722.12</v>
@@ -6960,7 +6960,7 @@
         <v>67</v>
       </c>
       <c r="P49">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q49">
         <v>5412.88</v>
@@ -7076,7 +7076,7 @@
         <v>3</v>
       </c>
       <c r="P50">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q50">
         <v>1024.2</v>
@@ -7192,7 +7192,7 @@
         <v>41</v>
       </c>
       <c r="P51">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Q51">
         <v>140.79</v>
@@ -7308,7 +7308,7 @@
         <v>9</v>
       </c>
       <c r="P52">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q52">
         <v>90.73999999999999</v>
@@ -7424,7 +7424,7 @@
         <v>11</v>
       </c>
       <c r="P53">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q53">
         <v>289.41</v>
@@ -7540,7 +7540,7 @@
         <v>26</v>
       </c>
       <c r="P54">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="Q54">
         <v>1048.14</v>
@@ -7772,7 +7772,7 @@
         <v>66</v>
       </c>
       <c r="P56">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Q56">
         <v>1225.36</v>
@@ -7888,7 +7888,7 @@
         <v>31</v>
       </c>
       <c r="P57">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q57">
         <v>397.1</v>
@@ -8120,7 +8120,7 @@
         <v>57</v>
       </c>
       <c r="P59">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Q59">
         <v>4069.72</v>
@@ -8236,7 +8236,7 @@
         <v>8</v>
       </c>
       <c r="P60">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="Q60">
         <v>3656.2</v>
@@ -8352,7 +8352,7 @@
         <v>34</v>
       </c>
       <c r="P61">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="Q61">
         <v>3123</v>
@@ -8584,7 +8584,7 @@
         <v>62</v>
       </c>
       <c r="P63">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="Q63">
         <v>1140.67</v>
@@ -8700,7 +8700,7 @@
         <v>20</v>
       </c>
       <c r="P64">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q64">
         <v>2534.9</v>
@@ -8932,7 +8932,7 @@
         <v>40</v>
       </c>
       <c r="P66">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q66">
         <v>2994.34</v>
@@ -9048,7 +9048,7 @@
         <v>82</v>
       </c>
       <c r="P67">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q67">
         <v>1444.96</v>
@@ -9164,7 +9164,7 @@
         <v>36</v>
       </c>
       <c r="P68">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q68">
         <v>357.14</v>
@@ -9396,7 +9396,7 @@
         <v>39</v>
       </c>
       <c r="P70">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Q70">
         <v>427.34</v>
@@ -9512,7 +9512,7 @@
         <v>73</v>
       </c>
       <c r="P71">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q71">
         <v>1595.2</v>
@@ -9628,7 +9628,7 @@
         <v>27</v>
       </c>
       <c r="P72">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q72">
         <v>106.37</v>
@@ -9744,7 +9744,7 @@
         <v>24</v>
       </c>
       <c r="P73">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q73">
         <v>287.55</v>
@@ -9860,7 +9860,7 @@
         <v>46</v>
       </c>
       <c r="P74">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q74">
         <v>366.76</v>
@@ -9976,7 +9976,7 @@
         <v>19</v>
       </c>
       <c r="P75">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q75">
         <v>1302.68</v>
@@ -10092,7 +10092,7 @@
         <v>23</v>
       </c>
       <c r="P76">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Q76">
         <v>1783.68</v>
@@ -10324,7 +10324,7 @@
         <v>32</v>
       </c>
       <c r="P78">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q78">
         <v>26184</v>
@@ -10556,7 +10556,7 @@
         <v>58</v>
       </c>
       <c r="P80">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q80">
         <v>3562.72</v>
@@ -10672,7 +10672,7 @@
         <v>85</v>
       </c>
       <c r="P81">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Q81">
         <v>18598.6</v>
@@ -10788,7 +10788,7 @@
         <v>70</v>
       </c>
       <c r="P82">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q82">
         <v>1881.86</v>
@@ -11002,7 +11002,7 @@
         <v>37</v>
       </c>
       <c r="P84">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q84">
         <v>1101.42</v>
@@ -11118,7 +11118,7 @@
         <v>17</v>
       </c>
       <c r="P85">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q85">
         <v>377.55</v>
@@ -11234,7 +11234,7 @@
         <v>50</v>
       </c>
       <c r="P86">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="Q86">
         <v>188.1</v>
@@ -11350,7 +11350,7 @@
         <v>4</v>
       </c>
       <c r="P87">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q87">
         <v>2053.84</v>
@@ -11466,7 +11466,7 @@
         <v>14</v>
       </c>
       <c r="P88">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q88">
         <v>1394.48</v>
@@ -11912,7 +11912,7 @@
         <v>91</v>
       </c>
       <c r="P92">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q92">
         <v>4691.78</v>
@@ -12028,7 +12028,7 @@
         <v>22</v>
       </c>
       <c r="P93">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q93">
         <v>3314.38</v>
@@ -12144,7 +12144,7 @@
         <v>71</v>
       </c>
       <c r="P94">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q94">
         <v>3567.24</v>
@@ -12260,7 +12260,7 @@
         <v>38</v>
       </c>
       <c r="P95">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="Q95">
         <v>11538.2</v>
@@ -12492,7 +12492,7 @@
         <v>52</v>
       </c>
       <c r="P97">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q97">
         <v>1372.56</v>
@@ -12608,7 +12608,7 @@
         <v>81</v>
       </c>
       <c r="P98">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q98">
         <v>513.1</v>
@@ -12724,7 +12724,7 @@
         <v>2</v>
       </c>
       <c r="P99">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Q99">
         <v>278.64</v>
@@ -12840,7 +12840,7 @@
         <v>6</v>
       </c>
       <c r="P100">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q100">
         <v>173.34</v>
@@ -12956,7 +12956,7 @@
         <v>88</v>
       </c>
       <c r="P101">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q101">
         <v>1116.7</v>

--- a/NIFTY_100_Technical_Metrics.xlsx
+++ b/NIFTY_100_Technical_Metrics.xlsx
@@ -1624,7 +1624,7 @@
         <v>99</v>
       </c>
       <c r="P3">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q3">
         <v>1541.46</v>
@@ -1740,7 +1740,7 @@
         <v>96</v>
       </c>
       <c r="P4">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="Q4">
         <v>3156.26</v>
@@ -1856,7 +1856,7 @@
         <v>98</v>
       </c>
       <c r="P5">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Q5">
         <v>1538.96</v>
@@ -1972,7 +1972,7 @@
         <v>92</v>
       </c>
       <c r="P6">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="Q6">
         <v>1858</v>
@@ -2088,7 +2088,7 @@
         <v>97</v>
       </c>
       <c r="P7">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q7">
         <v>223.75</v>
@@ -2204,7 +2204,7 @@
         <v>16</v>
       </c>
       <c r="P8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q8">
         <v>431.29</v>
@@ -2320,7 +2320,7 @@
         <v>86</v>
       </c>
       <c r="P9">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Q9">
         <v>8756.700000000001</v>
@@ -2436,7 +2436,7 @@
         <v>83</v>
       </c>
       <c r="P10">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q10">
         <v>2714.44</v>
@@ -2552,7 +2552,7 @@
         <v>61</v>
       </c>
       <c r="P11">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q11">
         <v>1352.24</v>
@@ -2784,7 +2784,7 @@
         <v>45</v>
       </c>
       <c r="P13">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q13">
         <v>1844.94</v>
@@ -2900,7 +2900,7 @@
         <v>30</v>
       </c>
       <c r="P14">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q14">
         <v>10867.6</v>
@@ -3016,7 +3016,7 @@
         <v>80</v>
       </c>
       <c r="P15">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q15">
         <v>1020.17</v>
@@ -3132,7 +3132,7 @@
         <v>29</v>
       </c>
       <c r="P16">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q16">
         <v>261.74</v>
@@ -3248,7 +3248,7 @@
         <v>25</v>
       </c>
       <c r="P17">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q17">
         <v>415.84</v>
@@ -3364,7 +3364,7 @@
         <v>33</v>
       </c>
       <c r="P18">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q18">
         <v>1883.76</v>
@@ -3480,7 +3480,7 @@
         <v>90</v>
       </c>
       <c r="P19">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="Q19">
         <v>41198</v>
@@ -3596,7 +3596,7 @@
         <v>47</v>
       </c>
       <c r="P20">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q20">
         <v>306.9</v>
@@ -3712,7 +3712,7 @@
         <v>21</v>
       </c>
       <c r="P21">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="Q21">
         <v>5308.1</v>
@@ -3828,7 +3828,7 @@
         <v>49</v>
       </c>
       <c r="P22">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q22">
         <v>126.56</v>
@@ -4060,7 +4060,7 @@
         <v>87</v>
       </c>
       <c r="P24">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q24">
         <v>1792.24</v>
@@ -4176,7 +4176,7 @@
         <v>59</v>
       </c>
       <c r="P25">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="Q25">
         <v>1458.9</v>
@@ -4292,7 +4292,7 @@
         <v>44</v>
       </c>
       <c r="P26">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q26">
         <v>438.02</v>
@@ -4408,7 +4408,7 @@
         <v>94</v>
       </c>
       <c r="P27">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Q27">
         <v>5571.4</v>
@@ -4640,7 +4640,7 @@
         <v>53</v>
       </c>
       <c r="P29">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q29">
         <v>655.75</v>
@@ -4872,7 +4872,7 @@
         <v>63</v>
       </c>
       <c r="P31">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q31">
         <v>1358.18</v>
@@ -5220,7 +5220,7 @@
         <v>72</v>
       </c>
       <c r="P34">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q34">
         <v>277.46</v>
@@ -5336,7 +5336,7 @@
         <v>56</v>
       </c>
       <c r="P35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="Q35">
         <v>174.29</v>
@@ -5452,7 +5452,7 @@
         <v>43</v>
       </c>
       <c r="P36">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="Q36">
         <v>1061.66</v>
@@ -5568,7 +5568,7 @@
         <v>79</v>
       </c>
       <c r="P37">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q37">
         <v>3160.7</v>
@@ -5684,7 +5684,7 @@
         <v>48</v>
       </c>
       <c r="P38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q38">
         <v>4421.48</v>
@@ -5800,7 +5800,7 @@
         <v>5</v>
       </c>
       <c r="P39">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q39">
         <v>1092.42</v>
@@ -5916,7 +5916,7 @@
         <v>78</v>
       </c>
       <c r="P40">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q40">
         <v>2751.8</v>
@@ -6148,7 +6148,7 @@
         <v>10</v>
       </c>
       <c r="P42">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q42">
         <v>570.51</v>
@@ -6264,7 +6264,7 @@
         <v>74</v>
       </c>
       <c r="P43">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Q43">
         <v>950.38</v>
@@ -6612,7 +6612,7 @@
         <v>42</v>
       </c>
       <c r="P46">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Q46">
         <v>1952.26</v>
@@ -6728,7 +6728,7 @@
         <v>54</v>
       </c>
       <c r="P47">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q47">
         <v>1395.56</v>
@@ -6844,7 +6844,7 @@
         <v>60</v>
       </c>
       <c r="P48">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q48">
         <v>722.12</v>
@@ -6960,7 +6960,7 @@
         <v>67</v>
       </c>
       <c r="P49">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q49">
         <v>5412.88</v>
@@ -7076,7 +7076,7 @@
         <v>3</v>
       </c>
       <c r="P50">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q50">
         <v>1024.2</v>
@@ -7192,7 +7192,7 @@
         <v>41</v>
       </c>
       <c r="P51">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="Q51">
         <v>140.79</v>
@@ -7308,7 +7308,7 @@
         <v>9</v>
       </c>
       <c r="P52">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q52">
         <v>90.73999999999999</v>
@@ -7424,7 +7424,7 @@
         <v>11</v>
       </c>
       <c r="P53">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q53">
         <v>289.41</v>
@@ -7540,7 +7540,7 @@
         <v>26</v>
       </c>
       <c r="P54">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q54">
         <v>1048.14</v>
@@ -7656,7 +7656,7 @@
         <v>12</v>
       </c>
       <c r="P55">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q55">
         <v>238.98</v>
@@ -7772,7 +7772,7 @@
         <v>66</v>
       </c>
       <c r="P56">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="Q56">
         <v>1225.36</v>
@@ -7888,7 +7888,7 @@
         <v>31</v>
       </c>
       <c r="P57">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Q57">
         <v>397.1</v>
@@ -8004,7 +8004,7 @@
         <v>77</v>
       </c>
       <c r="P58">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q58">
         <v>1013.55</v>
@@ -8236,7 +8236,7 @@
         <v>8</v>
       </c>
       <c r="P60">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="Q60">
         <v>3656.2</v>
@@ -8352,7 +8352,7 @@
         <v>34</v>
       </c>
       <c r="P61">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q61">
         <v>3123</v>
@@ -8468,7 +8468,7 @@
         <v>76</v>
       </c>
       <c r="P62">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="Q62">
         <v>14318</v>
@@ -8584,7 +8584,7 @@
         <v>62</v>
       </c>
       <c r="P63">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="Q63">
         <v>1140.67</v>
@@ -8932,7 +8932,7 @@
         <v>40</v>
       </c>
       <c r="P66">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q66">
         <v>2994.34</v>
@@ -9048,7 +9048,7 @@
         <v>82</v>
       </c>
       <c r="P67">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q67">
         <v>1444.96</v>
@@ -9280,7 +9280,7 @@
         <v>15</v>
       </c>
       <c r="P69">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q69">
         <v>236.31</v>
@@ -9396,7 +9396,7 @@
         <v>39</v>
       </c>
       <c r="P70">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q70">
         <v>427.34</v>
@@ -9512,7 +9512,7 @@
         <v>73</v>
       </c>
       <c r="P71">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Q71">
         <v>1595.2</v>
@@ -9628,7 +9628,7 @@
         <v>27</v>
       </c>
       <c r="P72">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="Q72">
         <v>106.37</v>
@@ -9860,7 +9860,7 @@
         <v>46</v>
       </c>
       <c r="P74">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q74">
         <v>366.76</v>
@@ -9976,7 +9976,7 @@
         <v>19</v>
       </c>
       <c r="P75">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q75">
         <v>1302.68</v>
@@ -10092,7 +10092,7 @@
         <v>23</v>
       </c>
       <c r="P76">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q76">
         <v>1783.68</v>
@@ -10208,7 +10208,7 @@
         <v>75</v>
       </c>
       <c r="P77">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q77">
         <v>1041.18</v>
@@ -10440,7 +10440,7 @@
         <v>93</v>
       </c>
       <c r="P79">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q79">
         <v>1056.83</v>
@@ -10556,7 +10556,7 @@
         <v>58</v>
       </c>
       <c r="P80">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Q80">
         <v>3562.72</v>
@@ -10672,7 +10672,7 @@
         <v>85</v>
       </c>
       <c r="P81">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q81">
         <v>18598.6</v>
@@ -10788,7 +10788,7 @@
         <v>70</v>
       </c>
       <c r="P82">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q82">
         <v>1881.86</v>
@@ -11002,7 +11002,7 @@
         <v>37</v>
       </c>
       <c r="P84">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q84">
         <v>1101.42</v>
@@ -11118,7 +11118,7 @@
         <v>17</v>
       </c>
       <c r="P85">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q85">
         <v>377.55</v>
@@ -11234,7 +11234,7 @@
         <v>50</v>
       </c>
       <c r="P86">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q86">
         <v>188.1</v>
@@ -11350,7 +11350,7 @@
         <v>4</v>
       </c>
       <c r="P87">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="Q87">
         <v>2053.84</v>
@@ -11466,7 +11466,7 @@
         <v>14</v>
       </c>
       <c r="P88">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="Q88">
         <v>1394.48</v>
@@ -11796,7 +11796,7 @@
         <v>7</v>
       </c>
       <c r="P91">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q91">
         <v>346.83</v>
@@ -11912,7 +11912,7 @@
         <v>91</v>
       </c>
       <c r="P92">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q92">
         <v>4691.78</v>
@@ -12028,7 +12028,7 @@
         <v>22</v>
       </c>
       <c r="P93">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q93">
         <v>3314.38</v>
@@ -12260,7 +12260,7 @@
         <v>38</v>
       </c>
       <c r="P95">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q95">
         <v>11538.2</v>
@@ -12376,7 +12376,7 @@
         <v>28</v>
       </c>
       <c r="P96">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q96">
         <v>168.57</v>
@@ -12492,7 +12492,7 @@
         <v>52</v>
       </c>
       <c r="P97">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q97">
         <v>1372.56</v>
@@ -12724,7 +12724,7 @@
         <v>2</v>
       </c>
       <c r="P99">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q99">
         <v>278.64</v>
@@ -12840,7 +12840,7 @@
         <v>6</v>
       </c>
       <c r="P100">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q100">
         <v>173.34</v>
